--- a/sheets/조재수대금교본/검수/가야지.xlsx
+++ b/sheets/조재수대금교본/검수/가야지.xlsx
@@ -5537,7 +5537,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲林∧
+          <t xml:space="preserve">仲林
 –</t>
         </is>
       </c>
@@ -5575,8 +5575,7 @@
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-黃
-ﾉ</t>
+黃</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -5585,17 +5584,9 @@
     </row>
     <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="23"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="23"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
@@ -5631,23 +5622,14 @@
         </is>
       </c>
       <c r="E6" s="24"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-黃
-‹</t>
+黃</t>
         </is>
       </c>
       <c r="K6" s="24"/>
@@ -5665,7 +5647,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南∧
+          <t xml:space="preserve">林南
 –</t>
         </is>
       </c>
@@ -5679,7 +5661,7 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南∧
+          <t xml:space="preserve">林南
 –</t>
         </is>
       </c>
@@ -5693,7 +5675,7 @@
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
+          <t xml:space="preserve">太
 仲</t>
         </is>
       </c>
@@ -5711,11 +5693,7 @@
         </is>
       </c>
       <c r="G8" s="23"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="23"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
@@ -5734,17 +5712,9 @@
     </row>
     <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B9" s="21"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="23"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
@@ -5783,37 +5753,27 @@
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲∼
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
     </row>
     <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -5827,7 +5787,7 @@
       <c r="E11" s="22"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南∧
+          <t xml:space="preserve">林南
 –</t>
         </is>
       </c>
@@ -5840,7 +5800,7 @@
       <c r="I11" s="22"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲林∧
+          <t xml:space="preserve">仲林
 –</t>
         </is>
       </c>
@@ -5863,12 +5823,7 @@
       <c r="G12" s="23"/>
       <c r="H12" s="21"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-‹</t>
-        </is>
-      </c>
+      <c r="J12" s="21"/>
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
@@ -5895,43 +5850,30 @@
         </is>
       </c>
       <c r="K13" s="23"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
     <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太太
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-仲ʒ</t>
+仲</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -5963,7 +5905,7 @@
       <c r="I15" s="22"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南∧
+          <t xml:space="preserve">林南
 –</t>
         </is>
       </c>
@@ -5994,11 +5936,7 @@
         </is>
       </c>
       <c r="I16" s="23"/>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J16" s="21"/>
       <c r="K16" s="23"/>
       <c r="L16" s="21"/>
       <c r="M16" s="23"/>
@@ -6043,15 +5981,14 @@
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∼
-‹</t>
+          <t xml:space="preserve">姑∼</t>
         </is>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲ʒ</t>
+仲</t>
         </is>
       </c>
       <c r="G18" s="24"/>
@@ -6069,11 +6006,7 @@
         </is>
       </c>
       <c r="K18" s="24"/>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L18" s="21"/>
       <c r="M18" s="24"/>
     </row>
     <row r="19" ht="6.0" customHeight="true">
@@ -6121,7 +6054,7 @@
       <c r="G21" s="22"/>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南∧
+          <t xml:space="preserve">林南
 –</t>
         </is>
       </c>
@@ -6168,17 +6101,9 @@
     </row>
     <row r="23" ht="91.25" customHeight="true">
       <c r="A23" s="0"/>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B23" s="21"/>
       <c r="C23" s="23"/>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D23" s="21"/>
       <c r="E23" s="23"/>
       <c r="F23" s="21" t="inlineStr">
         <is>
@@ -6214,24 +6139,14 @@
         </is>
       </c>
       <c r="E24" s="24"/>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F24" s="21"/>
       <c r="G24" s="24"/>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="H24" s="21"/>
       <c r="I24" s="24"/>
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-太
-‹</t>
+太</t>
         </is>
       </c>
       <c r="K24" s="24"/>
@@ -6249,21 +6164,21 @@
       <c r="C25" s="22"/>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應∧
+          <t xml:space="preserve">南應
 –</t>
         </is>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應∧
+          <t xml:space="preserve">南應
 –</t>
         </is>
       </c>
       <c r="G25" s="22"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應∧
+          <t xml:space="preserve">南應
 –∼</t>
         </is>
       </c>
@@ -6277,7 +6192,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∧
+          <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
@@ -6295,11 +6210,7 @@
         </is>
       </c>
       <c r="G26" s="23"/>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H26" s="21"/>
       <c r="I26" s="23"/>
       <c r="J26" s="21" t="inlineStr">
         <is>
@@ -6318,17 +6229,9 @@
     </row>
     <row r="27" ht="91.25" customHeight="true">
       <c r="A27" s="0"/>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B27" s="21"/>
       <c r="C27" s="23"/>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D27" s="21"/>
       <c r="E27" s="23"/>
       <c r="F27" s="21" t="inlineStr">
         <is>
@@ -6367,30 +6270,20 @@
       <c r="E28" s="24"/>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G28" s="24"/>
       <c r="H28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
     </row>
     <row r="29" ht="91.25" customHeight="true">
@@ -6398,7 +6291,6 @@
       <c r="B29" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-ﾉ
 㴌</t>
         </is>
       </c>
@@ -6412,7 +6304,7 @@
       <c r="E29" s="22"/>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應∧
+          <t xml:space="preserve">南應
 –</t>
         </is>
       </c>
@@ -6425,7 +6317,7 @@
       <c r="I29" s="22"/>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南∧
+          <t xml:space="preserve">林南
 –</t>
         </is>
       </c>
@@ -6448,16 +6340,11 @@
       <c r="G30" s="23"/>
       <c r="H30" s="21"/>
       <c r="I30" s="23"/>
-      <c r="J30" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-‹</t>
-        </is>
-      </c>
+      <c r="J30" s="21"/>
       <c r="K30" s="23"/>
       <c r="L30" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南∧
+          <t xml:space="preserve">林南
 –</t>
         </is>
       </c>
@@ -6480,47 +6367,30 @@
         </is>
       </c>
       <c r="K31" s="23"/>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L31" s="21"/>
       <c r="M31" s="23"/>
     </row>
     <row r="32" ht="91.25" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D32" s="21"/>
       <c r="E32" s="24"/>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F32" s="21"/>
       <c r="G32" s="24"/>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H32" s="21"/>
       <c r="I32" s="24"/>
       <c r="J32" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K32" s="24"/>
       <c r="L32" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">應南
-林ʒ</t>
+林</t>
         </is>
       </c>
       <c r="M32" s="24"/>
@@ -6552,7 +6422,7 @@
       <c r="I33" s="22"/>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應∧
+          <t xml:space="preserve">南應
 –</t>
         </is>
       </c>
@@ -6583,12 +6453,7 @@
         </is>
       </c>
       <c r="I34" s="23"/>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-‹</t>
-        </is>
-      </c>
+      <c r="J34" s="21"/>
       <c r="K34" s="23"/>
       <c r="L34" s="21"/>
       <c r="M34" s="23"/>
@@ -6633,39 +6498,32 @@
       <c r="C36" s="24"/>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∼
-‹</t>
+          <t xml:space="preserve">仲∼</t>
         </is>
       </c>
       <c r="E36" s="24"/>
       <c r="F36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林ʒ</t>
+林</t>
         </is>
       </c>
       <c r="G36" s="24"/>
       <c r="H36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I36" s="24"/>
       <c r="J36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K36" s="24"/>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L36" s="21"/>
       <c r="M36" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/가야지.xlsx
+++ b/sheets/조재수대금교본/검수/가야지.xlsx
@@ -5537,7 +5537,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲林
+          <t xml:space="preserve">仲林∧
 –</t>
         </is>
       </c>
@@ -5575,7 +5575,8 @@
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-黃</t>
+黃
+ﾉ</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -5647,7 +5648,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南∧
 –</t>
         </is>
       </c>
@@ -5661,7 +5662,7 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南∧
 –</t>
         </is>
       </c>
@@ -5675,7 +5676,7 @@
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太∧
 仲</t>
         </is>
       </c>
@@ -5773,7 +5774,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–ﾉ
 汰</t>
         </is>
       </c>
@@ -5787,7 +5788,7 @@
       <c r="E11" s="22"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南∧
 –</t>
         </is>
       </c>
@@ -5800,7 +5801,7 @@
       <c r="I11" s="22"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲林
+          <t xml:space="preserve">仲林∧
 –</t>
         </is>
       </c>
@@ -5823,7 +5824,11 @@
       <c r="G12" s="23"/>
       <c r="H12" s="21"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="21"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
@@ -5850,7 +5855,11 @@
         </is>
       </c>
       <c r="K13" s="23"/>
-      <c r="L13" s="21"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M13" s="23"/>
     </row>
     <row r="14" ht="91.25" customHeight="true">
@@ -5873,7 +5882,7 @@
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-仲</t>
+仲ʒ</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -5905,7 +5914,7 @@
       <c r="I15" s="22"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南∧
 –</t>
         </is>
       </c>
@@ -5936,7 +5945,11 @@
         </is>
       </c>
       <c r="I16" s="23"/>
-      <c r="J16" s="21"/>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K16" s="23"/>
       <c r="L16" s="21"/>
       <c r="M16" s="23"/>
@@ -5988,7 +6001,7 @@
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲</t>
+仲ʒ</t>
         </is>
       </c>
       <c r="G18" s="24"/>
@@ -6054,7 +6067,7 @@
       <c r="G21" s="22"/>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南∧
 –</t>
         </is>
       </c>
@@ -6141,7 +6154,11 @@
       <c r="E24" s="24"/>
       <c r="F24" s="21"/>
       <c r="G24" s="24"/>
-      <c r="H24" s="21"/>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I24" s="24"/>
       <c r="J24" s="21" t="inlineStr">
         <is>
@@ -6164,21 +6181,21 @@
       <c r="C25" s="22"/>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應
+          <t xml:space="preserve">南應∧
 –</t>
         </is>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應
+          <t xml:space="preserve">南應∧
 –</t>
         </is>
       </c>
       <c r="G25" s="22"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應
+          <t xml:space="preserve">南應∧
 –∼</t>
         </is>
       </c>
@@ -6192,7 +6209,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
+          <t xml:space="preserve">姑∧
 林</t>
         </is>
       </c>
@@ -6291,6 +6308,7 @@
       <c r="B29" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
+ﾉ
 㴌</t>
         </is>
       </c>
@@ -6304,7 +6322,7 @@
       <c r="E29" s="22"/>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應
+          <t xml:space="preserve">南應∧
 –</t>
         </is>
       </c>
@@ -6317,7 +6335,7 @@
       <c r="I29" s="22"/>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南∧
 –</t>
         </is>
       </c>
@@ -6340,11 +6358,15 @@
       <c r="G30" s="23"/>
       <c r="H30" s="21"/>
       <c r="I30" s="23"/>
-      <c r="J30" s="21"/>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K30" s="23"/>
       <c r="L30" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南∧
 –</t>
         </is>
       </c>
@@ -6367,7 +6389,11 @@
         </is>
       </c>
       <c r="K31" s="23"/>
-      <c r="L31" s="21"/>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M31" s="23"/>
     </row>
     <row r="32" ht="91.25" customHeight="true">
@@ -6390,7 +6416,7 @@
       <c r="L32" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">應南
-林</t>
+林ʒ</t>
         </is>
       </c>
       <c r="M32" s="24"/>
@@ -6422,7 +6448,7 @@
       <c r="I33" s="22"/>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南應
+          <t xml:space="preserve">南應∧
 –</t>
         </is>
       </c>
@@ -6453,7 +6479,11 @@
         </is>
       </c>
       <c r="I34" s="23"/>
-      <c r="J34" s="21"/>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K34" s="23"/>
       <c r="L34" s="21"/>
       <c r="M34" s="23"/>
@@ -6505,7 +6535,7 @@
       <c r="F36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林</t>
+林ʒ</t>
         </is>
       </c>
       <c r="G36" s="24"/>

--- a/sheets/조재수대금교본/검수/가야지.xlsx
+++ b/sheets/조재수대금교본/검수/가야지.xlsx
@@ -5478,17 +5478,17 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
